--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA75E24C-B361-4793-A74B-9548E826E1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A86AFF-23A3-4D03-9F4A-C3CF041DFE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -767,35 +767,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="13" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="13" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -828,11 +801,38 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="13" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1201,62 +1201,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="53"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="42"/>
     </row>
     <row r="2" spans="1:16" ht="21.75" thickBot="1">
-      <c r="A2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="45"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1"/>
     <row r="4" spans="1:16" ht="27" thickBot="1">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="59"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="48"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" thickBot="1">
       <c r="A5" s="1"/>
@@ -1275,87 +1275,87 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="46" t="s">
+      <c r="I6" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="45" t="s">
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="42" t="s">
+      <c r="N6" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="48" t="s">
+      <c r="O6" s="37" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="36"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="43" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="43" t="s">
+      <c r="K7" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="44" t="s">
+      <c r="L7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="49"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="50"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="39"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="17" t="s">
@@ -1573,7 +1573,7 @@
       <c r="N13" s="4">
         <v>30000</v>
       </c>
-      <c r="O13" s="61"/>
+      <c r="O13" s="35"/>
       <c r="P13" s="33"/>
     </row>
     <row r="14" spans="1:16">
@@ -1691,17 +1691,17 @@
         <v>31</v>
       </c>
       <c r="J16" s="10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K16" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L16" s="10">
         <v>1</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="4">
-        <v>17420</v>
+        <v>15677.42</v>
       </c>
       <c r="O16" s="20"/>
       <c r="P16" s="33"/>
@@ -1747,7 +1747,7 @@
       <c r="N17" s="27">
         <v>27097</v>
       </c>
-      <c r="O17" s="62"/>
+      <c r="O17" s="36"/>
       <c r="P17" s="3"/>
     </row>
     <row r="18" spans="1:16">
@@ -1783,23 +1783,23 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="27" thickBot="1">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="59"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="48"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
@@ -1818,87 +1818,87 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="41" t="s">
+      <c r="G22" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="60" t="s">
+      <c r="I22" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
-      <c r="M22" s="45" t="s">
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="N22" s="42" t="s">
+      <c r="N22" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="O22" s="48" t="s">
+      <c r="O22" s="37" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A23" s="36"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="43" t="s">
+      <c r="A23" s="53"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="43" t="s">
+      <c r="J23" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="43" t="s">
+      <c r="K23" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="44" t="s">
+      <c r="L23" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="49"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A24" s="37"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="50"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="39"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1">
       <c r="A25" s="17" t="s">
@@ -2322,6 +2322,26 @@
     <row r="97" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
     <mergeCell ref="O6:O8"/>
     <mergeCell ref="O22:O24"/>
     <mergeCell ref="A1:O1"/>
@@ -2338,38 +2358,18 @@
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="F22:F24"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
   </mergeCells>
-  <conditionalFormatting sqref="B25 B9:M9 B27:B31 D10:M16 C11:C16">
-    <cfRule type="expression" dxfId="2" priority="5">
+  <conditionalFormatting sqref="B10:C10 D17:L17 B25:M25">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$C10=#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:M9 D10:M16 C11:C16 B27:B31">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10:C10 C25:M25 D17:L17 C32:M32 M26 C26:H31 K27:M31 J26:J31">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$C10=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I31 K26:L26">
+  <conditionalFormatting sqref="C26:M32">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C26=#REF!</formula>
     </cfRule>

--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A86AFF-23A3-4D03-9F4A-C3CF041DFE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7E183D-4A16-4510-9D0F-76A6F6897EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="91">
   <si>
     <t xml:space="preserve">Government High School Sindhi Jamaat Cooperative Housing Society, Bin Qasim Town Karachi </t>
   </si>
@@ -261,9 +261,6 @@
     <t>Rimsha Bibi</t>
   </si>
   <si>
-    <t>31201 2460819 2</t>
-  </si>
-  <si>
     <t>LHV</t>
   </si>
   <si>
@@ -295,6 +292,21 @@
   </si>
   <si>
     <t>43504-0807335-4</t>
+  </si>
+  <si>
+    <t>31201-2460819-2</t>
+  </si>
+  <si>
+    <t>Samina</t>
+  </si>
+  <si>
+    <t>Father Name / Husband Name</t>
+  </si>
+  <si>
+    <t>Muhammad Ishaq</t>
+  </si>
+  <si>
+    <t>42501-3508487-6</t>
   </si>
 </sst>
 </file>
@@ -400,7 +412,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -681,11 +693,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -769,6 +820,35 @@
     <xf numFmtId="13" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="13" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -801,36 +881,42 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -883,8 +969,8 @@
       <sheetName val="Salary Sheet"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1182,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -1201,62 +1287,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21">
-      <c r="A1" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="42"/>
+      <c r="A1" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="55"/>
     </row>
     <row r="2" spans="1:16" ht="21.75" thickBot="1">
-      <c r="A2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="45"/>
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="58"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1"/>
     <row r="4" spans="1:16" ht="27" thickBot="1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="48"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="61"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" thickBot="1">
       <c r="A5" s="1"/>
@@ -1275,87 +1361,87 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="61" t="s">
+      <c r="I6" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="59" t="s">
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="57" t="s">
+      <c r="N6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="37" t="s">
-        <v>79</v>
+      <c r="O6" s="50" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="53"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="60" t="s">
+      <c r="A7" s="38"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="60" t="s">
+      <c r="J7" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="62" t="s">
+      <c r="L7" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="38"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="51"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A8" s="54"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="39"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="52"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="17" t="s">
@@ -1578,10 +1664,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="29" t="s">
         <v>80</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>81</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>19</v>
@@ -1593,7 +1679,7 @@
         <v>45770</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>34</v>
@@ -1621,10 +1707,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>19</v>
@@ -1636,7 +1722,7 @@
         <v>45779</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>34</v>
@@ -1664,10 +1750,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>19</v>
@@ -1679,7 +1765,7 @@
         <v>45712</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>34</v>
@@ -1783,23 +1869,23 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="27" thickBot="1">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="48"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="61"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
@@ -1818,87 +1904,87 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="49" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="49" t="s">
+      <c r="B22" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="58" t="s">
+      <c r="G22" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="58" t="s">
+      <c r="H22" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="55" t="s">
+      <c r="I22" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="56"/>
-      <c r="M22" s="59" t="s">
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="N22" s="57" t="s">
+      <c r="N22" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="O22" s="37" t="s">
-        <v>79</v>
+      <c r="O22" s="50" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="60" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="60" t="s">
+      <c r="J23" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="60" t="s">
+      <c r="K23" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="62" t="s">
+      <c r="L23" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="38"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="51"/>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A24" s="54"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="39"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="52"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1">
       <c r="A25" s="17" t="s">
@@ -1953,7 +2039,7 @@
         <v>40</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>20</v>
@@ -2020,11 +2106,9 @@
         <v>31</v>
       </c>
       <c r="K27" s="5">
-        <f>[1]Attandance!AJ20</f>
         <v>0</v>
       </c>
       <c r="L27" s="5">
-        <f>[1]Attandance!AK20</f>
         <v>0</v>
       </c>
       <c r="M27" s="5"/>
@@ -2065,11 +2149,9 @@
         <v>31</v>
       </c>
       <c r="K28" s="5">
-        <f>[1]Attandance!AJ21</f>
         <v>0</v>
       </c>
       <c r="L28" s="5">
-        <f>[1]Attandance!AK21</f>
         <v>0</v>
       </c>
       <c r="M28" s="5"/>
@@ -2153,11 +2235,9 @@
         <v>31</v>
       </c>
       <c r="K30" s="5">
-        <f>[1]Attandance!AJ23</f>
         <v>0</v>
       </c>
       <c r="L30" s="5">
-        <f>[1]Attandance!AK23</f>
         <v>0</v>
       </c>
       <c r="M30" s="5"/>
@@ -2198,7 +2278,6 @@
         <v>31</v>
       </c>
       <c r="K31" s="5">
-        <f>[1]Attandance!AJ24</f>
         <v>0</v>
       </c>
       <c r="L31" s="5">
@@ -2210,67 +2289,111 @@
       </c>
       <c r="O31" s="20"/>
     </row>
-    <row r="32" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A32" s="21" t="s">
+    <row r="32" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A32" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="64">
         <v>44959</v>
       </c>
-      <c r="F32" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G32" s="25" t="s">
+      <c r="F32" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="65">
         <v>16500</v>
       </c>
-      <c r="I32" s="22">
-        <v>31</v>
-      </c>
-      <c r="J32" s="22">
-        <v>31</v>
-      </c>
-      <c r="K32" s="22">
+      <c r="I32" s="10">
+        <v>31</v>
+      </c>
+      <c r="J32" s="10">
+        <v>31</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="63">
+        <v>0</v>
+      </c>
+      <c r="M32" s="63"/>
+      <c r="N32" s="66">
+        <v>16500</v>
+      </c>
+      <c r="O32" s="67"/>
+    </row>
+    <row r="33" spans="1:15" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A33" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="23">
+        <v>45767</v>
+      </c>
+      <c r="F33" s="75" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="26">
+        <v>15000</v>
+      </c>
+      <c r="I33" s="22">
+        <v>40</v>
+      </c>
+      <c r="J33" s="22">
+        <v>40</v>
+      </c>
+      <c r="K33" s="22">
         <f>[1]Attandance!AJ25</f>
         <v>0</v>
       </c>
-      <c r="L32" s="22">
+      <c r="L33" s="22">
         <f>[1]Attandance!AK25</f>
         <v>0</v>
       </c>
-      <c r="M32" s="22"/>
-      <c r="N32" s="27">
-        <v>16500</v>
-      </c>
-      <c r="O32" s="28"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="27">
+        <v>20000</v>
+      </c>
+      <c r="O33" s="28"/>
+    </row>
+    <row r="34" spans="1:15" ht="15.75" customHeight="1">
+      <c r="O34" s="33"/>
+    </row>
+    <row r="35" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2320,28 +2443,9 @@
     <row r="95" ht="15.75" customHeight="1"/>
     <row r="96" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
     <mergeCell ref="O6:O8"/>
     <mergeCell ref="O22:O24"/>
     <mergeCell ref="A1:O1"/>
@@ -2358,18 +2462,38 @@
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="F22:F24"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:C10 D17:L17 B25:M25">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$C10=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:M9 D10:M16 C11:C16 B27:B31">
+  <conditionalFormatting sqref="B9:M9 D10:M16 C11:C16 B27:B32">
     <cfRule type="expression" dxfId="1" priority="5">
       <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26:M32">
+  <conditionalFormatting sqref="C26:M33">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C26=#REF!</formula>
     </cfRule>

--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7E183D-4A16-4510-9D0F-76A6F6897EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260CE897-B0A6-4FFB-9751-DD2FD34811EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="94">
   <si>
     <t xml:space="preserve">Government High School Sindhi Jamaat Cooperative Housing Society, Bin Qasim Town Karachi </t>
   </si>
@@ -307,6 +304,15 @@
   </si>
   <si>
     <t>42501-3508487-6</t>
+  </si>
+  <si>
+    <t>Arif Panhwar</t>
+  </si>
+  <si>
+    <t>Ghulam Muhammad Panhwar</t>
+  </si>
+  <si>
+    <t>41406-5814423-9</t>
   </si>
 </sst>
 </file>
@@ -412,7 +418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -732,11 +738,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -820,103 +837,106 @@
     <xf numFmtId="13" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="13" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -959,21 +979,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Attandance"/>
-      <sheetName val="Salary Sheet"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1268,11 +1273,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
@@ -1287,62 +1292,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="55"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="53"/>
     </row>
     <row r="2" spans="1:16" ht="21.75" thickBot="1">
-      <c r="A2" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="58"/>
+      <c r="A2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="56"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1"/>
     <row r="4" spans="1:16" ht="27" thickBot="1">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="61"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="59"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" thickBot="1">
       <c r="A5" s="1"/>
@@ -1361,87 +1366,87 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="48" t="s">
+      <c r="I6" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="47" t="s">
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="44" t="s">
+      <c r="N6" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="50" t="s">
+      <c r="O6" s="48" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="38"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="45" t="s">
+      <c r="A7" s="64"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="45" t="s">
+      <c r="J7" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="45" t="s">
+      <c r="K7" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="46" t="s">
+      <c r="L7" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="51"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="49"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A8" s="39"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="52"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="50"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="17" t="s">
@@ -1869,23 +1874,23 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="27" thickBot="1">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="61"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="59"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
@@ -1904,87 +1909,87 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="43" t="s">
+      <c r="F22" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="43" t="s">
+      <c r="G22" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="62" t="s">
+      <c r="I22" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="47" t="s">
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="N22" s="44" t="s">
+      <c r="N22" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="O22" s="50" t="s">
+      <c r="O22" s="48" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A23" s="38"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="45" t="s">
+      <c r="A23" s="64"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="45" t="s">
+      <c r="J23" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="45" t="s">
+      <c r="K23" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="46" t="s">
+      <c r="L23" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="41"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="51"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="49"/>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A24" s="39"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="52"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="62"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="50"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1">
       <c r="A25" s="17" t="s">
@@ -2290,28 +2295,28 @@
       <c r="O31" s="20"/>
     </row>
     <row r="32" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A32" s="68" t="s">
+      <c r="A32" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="43" t="s">
         <v>65</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="64">
+      <c r="E32" s="38">
         <v>44959</v>
       </c>
-      <c r="F32" s="70" t="s">
+      <c r="F32" s="44" t="s">
         <v>86</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="65">
+      <c r="H32" s="39">
         <v>16500</v>
       </c>
       <c r="I32" s="10">
@@ -2323,64 +2328,104 @@
       <c r="K32" s="5">
         <v>0</v>
       </c>
-      <c r="L32" s="63">
-        <v>0</v>
-      </c>
-      <c r="M32" s="63"/>
-      <c r="N32" s="66">
+      <c r="L32" s="37">
+        <v>0</v>
+      </c>
+      <c r="M32" s="37"/>
+      <c r="N32" s="40">
         <v>16500</v>
       </c>
-      <c r="O32" s="67"/>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A33" s="71" t="s">
+      <c r="O32" s="41"/>
+    </row>
+    <row r="33" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A33" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="74" t="s">
+      <c r="B33" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="74" t="s">
+      <c r="C33" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="38">
         <v>45767</v>
       </c>
-      <c r="F33" s="75" t="s">
+      <c r="F33" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="39">
         <v>15000</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="76">
         <v>40</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33" s="76">
         <v>40</v>
       </c>
-      <c r="K33" s="22">
-        <f>[1]Attandance!AJ25</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="22">
-        <f>[1]Attandance!AK25</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="22"/>
-      <c r="N33" s="27">
+      <c r="K33" s="37">
+        <v>0</v>
+      </c>
+      <c r="L33" s="37">
+        <v>0</v>
+      </c>
+      <c r="M33" s="37"/>
+      <c r="N33" s="40">
         <v>20000</v>
       </c>
-      <c r="O33" s="28"/>
-    </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1">
-      <c r="O34" s="33"/>
-    </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1"/>
+      <c r="O33" s="41"/>
+    </row>
+    <row r="34" spans="1:15" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A34" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="23">
+        <v>45778</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="G34" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" s="26">
+        <v>15000</v>
+      </c>
+      <c r="I34" s="22">
+        <v>31</v>
+      </c>
+      <c r="J34" s="22">
+        <v>31</v>
+      </c>
+      <c r="K34" s="22">
+        <v>0</v>
+      </c>
+      <c r="L34" s="22">
+        <v>0</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="27">
+        <v>20000</v>
+      </c>
+      <c r="O34" s="28"/>
+    </row>
+    <row r="35" spans="1:15" ht="15.75" customHeight="1">
+      <c r="O35" s="33"/>
+    </row>
     <row r="36" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="38" spans="1:15" ht="15.75" customHeight="1"/>
@@ -2444,8 +2489,29 @@
     <row r="96" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
     <mergeCell ref="O6:O8"/>
     <mergeCell ref="O22:O24"/>
     <mergeCell ref="A1:O1"/>
@@ -2462,43 +2528,26 @@
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="F22:F24"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:C10 D17:L17 B25:M25">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$C10=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:M9 D10:M16 C11:C16 B27:B32">
+  <conditionalFormatting sqref="B9:M9 D10:M16 C11:C16 B27:B33">
     <cfRule type="expression" dxfId="1" priority="5">
       <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26:M33">
+  <conditionalFormatting sqref="C26:M34">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C26=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <ignoredErrors>
+    <ignoredError sqref="G25:G28 G9:G11" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - May-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260CE897-B0A6-4FFB-9751-DD2FD34811EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD0CE09-6D9C-473C-A48D-B2DD9DB25410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -279,9 +279,6 @@
     <t>43504-0807333-8</t>
   </si>
   <si>
-    <t>Salary Sheet for the Month May 2025</t>
-  </si>
-  <si>
     <t>Tasneem</t>
   </si>
   <si>
@@ -313,6 +310,9 @@
   </si>
   <si>
     <t>41406-5814423-9</t>
+  </si>
+  <si>
+    <t>Salary Sheet for the Month June 2025</t>
   </si>
 </sst>
 </file>
@@ -418,7 +418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -749,11 +749,148 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -866,6 +1003,63 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -903,40 +1097,52 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1273,81 +1479,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P99"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.42578125" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
     <col min="11" max="12" width="5.85546875" customWidth="1"/>
     <col min="13" max="14" width="11.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21">
-      <c r="A1" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="53"/>
+      <c r="A1" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="72"/>
     </row>
     <row r="2" spans="1:16" ht="21.75" thickBot="1">
-      <c r="A2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="75"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1"/>
     <row r="4" spans="1:16" ht="27" thickBot="1">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="59"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="78"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" thickBot="1">
       <c r="A5" s="1"/>
@@ -1366,87 +1575,87 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="66" t="s">
+      <c r="E6" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="66" t="s">
+      <c r="G6" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="66" t="s">
+      <c r="H6" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="74" t="s">
+      <c r="I6" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="72" t="s">
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="71" t="s">
+      <c r="N6" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="48" t="s">
+      <c r="O6" s="67" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="64"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="73" t="s">
+      <c r="A7" s="94"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="73" t="s">
+      <c r="J7" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="73" t="s">
+      <c r="K7" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="75" t="s">
+      <c r="L7" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="49"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="68"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="50"/>
+      <c r="A8" s="95"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="69"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="17" t="s">
@@ -1712,7 +1921,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="29" t="s">
         <v>80</v>
@@ -1727,7 +1936,7 @@
         <v>45779</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>34</v>
@@ -1755,7 +1964,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>76</v>
@@ -1874,23 +2083,23 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="27" thickBot="1">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="59"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="78"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="1"/>
@@ -1909,89 +2118,89 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="60" t="s">
+      <c r="B22" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="60" t="s">
+      <c r="D22" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="66" t="s">
+      <c r="E22" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="66" t="s">
+      <c r="G22" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="66" t="s">
+      <c r="H22" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="69" t="s">
+      <c r="I22" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="72" t="s">
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="N22" s="71" t="s">
+      <c r="N22" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="O22" s="48" t="s">
+      <c r="O22" s="55" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A23" s="64"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="73" t="s">
+      <c r="A23" s="53"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="73" t="s">
+      <c r="J23" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="73" t="s">
+      <c r="K23" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="75" t="s">
+      <c r="L23" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="49"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="56"/>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A24" s="65"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="62"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="50"/>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A24" s="54"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="57"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="17" t="s">
         <v>48</v>
       </c>
@@ -2079,7 +2288,7 @@
       </c>
       <c r="O26" s="20"/>
     </row>
-    <row r="27" spans="1:16" ht="15.75" customHeight="1">
+    <row r="27" spans="1:16">
       <c r="A27" s="19" t="s">
         <v>53</v>
       </c>
@@ -2122,7 +2331,7 @@
       </c>
       <c r="O27" s="20"/>
     </row>
-    <row r="28" spans="1:16" ht="15.75" customHeight="1">
+    <row r="28" spans="1:16">
       <c r="A28" s="19" t="s">
         <v>58</v>
       </c>
@@ -2165,7 +2374,7 @@
       </c>
       <c r="O28" s="20"/>
     </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1">
+    <row r="29" spans="1:16">
       <c r="A29" s="19" t="s">
         <v>63</v>
       </c>
@@ -2208,7 +2417,7 @@
       </c>
       <c r="O29" s="20"/>
     </row>
-    <row r="30" spans="1:16" ht="15.75" customHeight="1">
+    <row r="30" spans="1:16">
       <c r="A30" s="19" t="s">
         <v>67</v>
       </c>
@@ -2251,7 +2460,7 @@
       </c>
       <c r="O30" s="20"/>
     </row>
-    <row r="31" spans="1:16" ht="15.75" customHeight="1">
+    <row r="31" spans="1:16">
       <c r="A31" s="19" t="s">
         <v>71</v>
       </c>
@@ -2294,7 +2503,7 @@
       </c>
       <c r="O31" s="20"/>
     </row>
-    <row r="32" spans="1:16" ht="15.75" customHeight="1">
+    <row r="32" spans="1:16">
       <c r="A32" s="42" t="s">
         <v>74</v>
       </c>
@@ -2311,7 +2520,7 @@
         <v>44959</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>34</v>
@@ -2337,12 +2546,12 @@
       </c>
       <c r="O32" s="41"/>
     </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1">
+    <row r="33" spans="1:15">
       <c r="A33" s="42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" s="43" t="s">
         <v>69</v>
@@ -2351,10 +2560,10 @@
         <v>20</v>
       </c>
       <c r="E33" s="38">
-        <v>45767</v>
+        <v>45768</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>34</v>
@@ -2362,10 +2571,10 @@
       <c r="H33" s="39">
         <v>15000</v>
       </c>
-      <c r="I33" s="76">
+      <c r="I33" s="48">
         <v>40</v>
       </c>
-      <c r="J33" s="76">
+      <c r="J33" s="48">
         <v>40</v>
       </c>
       <c r="K33" s="37">
@@ -2380,12 +2589,12 @@
       </c>
       <c r="O33" s="41"/>
     </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1" thickBot="1">
+    <row r="34" spans="1:15" ht="15.75" thickBot="1">
       <c r="A34" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="46" t="s">
         <v>91</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>92</v>
       </c>
       <c r="C34" s="46" t="s">
         <v>55</v>
@@ -2397,13 +2606,13 @@
         <v>45778</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G34" s="25" t="s">
         <v>34</v>
       </c>
       <c r="H34" s="26">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="I34" s="22">
         <v>31</v>
@@ -2419,7 +2628,7 @@
       </c>
       <c r="M34" s="22"/>
       <c r="N34" s="27">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="O34" s="28"/>
     </row>
@@ -2492,41 +2701,41 @@
     <row r="99" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
     <mergeCell ref="O6:O8"/>
-    <mergeCell ref="O22:O24"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A4:O4"/>
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="O22:O24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="N22:N24"/>
     <mergeCell ref="I22:L22"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
     <mergeCell ref="F22:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:C10 D17:L17 B25:M25">
@@ -2544,8 +2753,8 @@
       <formula>$C26=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="G25:G28 G9:G11" numberStoredAsText="1"/>
   </ignoredErrors>
